--- a/PHARMA.xlsx
+++ b/PHARMA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="135">
   <si>
     <t>NO</t>
   </si>
@@ -425,6 +425,18 @@
   </si>
   <si>
     <t>NIKHIL PATEL</t>
+  </si>
+  <si>
+    <t>ARISTO PHARMA</t>
+  </si>
+  <si>
+    <t>PARESH THAKER</t>
+  </si>
+  <si>
+    <t>NIRANJAN DASANI</t>
+  </si>
+  <si>
+    <t>DHIRAJKUMAR</t>
   </si>
 </sst>
 </file>
@@ -468,7 +480,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -491,34 +503,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -533,8 +528,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1016,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -1029,1295 +1031,1337 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18.75">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.75">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>8849816883</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18.75">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>7359409431</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18.75">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>7990789429</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18.75">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>9429317767</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18.75">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>9408233766</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18.75">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>9601424209</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18.75">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>8905223389</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18.75">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>9727783932</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18.75">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>8200177545</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18.75">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <v>9714712264</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18.75">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <v>9033399564</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18.75">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <v>8140317118</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <v>9601793913</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18.75">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>9099661345</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="3">
         <v>7600631604</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18.75">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="3">
         <v>8780856496</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="3">
         <v>9377661345</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18.75">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="3">
         <v>9586299911</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18.75">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="3">
         <v>9825748241</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18.75">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18.75">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="3">
         <v>9909006684</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.75">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="3">
         <v>9909026634</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18.75">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="3">
         <v>8758671797</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18.75">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="3">
         <v>9662779020</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75">
-      <c r="A28" s="4">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="3">
         <v>9558780330</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18.75">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="3">
         <v>9638030812</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18.75">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="3">
         <v>6355485050</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18.75">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="3">
         <v>7600459222</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18.75">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="3">
         <v>9725057586</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18.75">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="3">
         <v>9099928060</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18.75">
-      <c r="A34" s="4">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="3">
         <v>8140814093</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18.75">
-      <c r="A35" s="4">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="3">
         <v>9510882026</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18.75">
-      <c r="A36" s="4">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="3">
         <v>8511746611</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18.75">
-      <c r="A37" s="4">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="3">
         <v>9099041004</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18.75">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="3">
         <v>9429347065</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18.75">
-      <c r="A39" s="4">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="3">
         <v>9537515515</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18.75">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="3">
         <v>9998326804</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75">
-      <c r="A41" s="4">
+      <c r="A41" s="2">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="3">
         <v>9979861157</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="3">
         <v>9979953555</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18.75">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="3">
         <v>7096127811</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75">
-      <c r="A44" s="4">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="3">
         <v>9638725303</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18.75">
-      <c r="A45" s="4">
+      <c r="A45" s="2">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="3">
         <v>8155005405</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75">
-      <c r="A46" s="4">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="3">
         <v>7665601410</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18.75">
-      <c r="A47" s="4">
+      <c r="A47" s="2">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="3">
         <v>9023868821</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18.75">
-      <c r="A48" s="4">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="3">
         <v>9737371486</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75">
-      <c r="A49" s="4">
+      <c r="A49" s="2">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="3">
         <v>9428948866</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75">
-      <c r="A50" s="4">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="3">
         <v>9998800079</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75">
-      <c r="A51" s="4">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75">
-      <c r="A52" s="4">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18.75">
-      <c r="A53" s="4">
+      <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18.75">
-      <c r="A54" s="4">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="3">
         <v>8238372625</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18.75">
-      <c r="A55" s="4">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="3">
         <v>9016625687</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18.75">
-      <c r="A56" s="4">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="3">
         <v>7728883118</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18.75">
-      <c r="A57" s="4">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="3">
         <v>9998900330</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18.75">
-      <c r="A58" s="4">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="3">
         <v>9979887992</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18.75">
-      <c r="A59" s="4">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18.75">
-      <c r="A60" s="4">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18.75">
-      <c r="A61" s="4">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="3">
         <v>9925171610</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="18.75">
-      <c r="A62" s="4">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="3">
         <v>9879607422</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18.75">
-      <c r="A63" s="4">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="3">
         <v>9727768173</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18.75">
-      <c r="A64" s="4">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="3">
         <v>9727713871</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="18.75">
-      <c r="A65" s="4">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="3" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18.75">
-      <c r="A66" s="4">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="3">
         <v>9723553601</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18.75">
-      <c r="A67" s="4">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="3">
         <v>9033301948</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="18.75">
-      <c r="A68" s="4">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="3">
         <v>8511154494</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="18.75">
-      <c r="A69" s="4">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="3">
         <v>8655924713</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="18.75">
-      <c r="A70" s="4">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="3">
         <v>9099304021</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="18.75">
-      <c r="A71" s="4">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="3">
         <v>6351930489</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="18.75">
-      <c r="A72" s="4">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="3">
         <v>8347912781</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="18.75">
-      <c r="A73" s="4">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="3">
         <v>7016839757</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="18.75">
-      <c r="A74" s="4">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="3">
         <v>8866265062</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="18.75">
-      <c r="A75" s="4">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="3">
         <v>9722435747</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="18.75">
-      <c r="A76" s="4">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="3">
         <v>7874929252</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="18.75">
-      <c r="A77" s="4">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="3">
         <v>9537742166</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="18.75">
-      <c r="A78" s="4">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="3">
         <v>9427607958</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="18.75">
-      <c r="A79" s="4">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="3" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="18.75">
-      <c r="A80" s="4">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="3">
         <v>9033495028</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="18.75">
-      <c r="A81" s="4">
+      <c r="A81" s="2">
         <v>80</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="3">
         <v>8866167939</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="21">
-      <c r="A82" s="4">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D82" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="21">
-      <c r="A83" s="4">
+      <c r="A83" s="2">
         <v>82</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="7">
         <v>9898497495</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="21">
-      <c r="A84" s="4">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="7">
         <v>7878001341</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="21">
-      <c r="A85" s="4">
+      <c r="A85" s="2">
         <v>84</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="7">
         <v>9726678123</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="21">
-      <c r="A86" s="4">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="3">
         <v>9924077117</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="21">
-      <c r="A87" s="4">
+      <c r="A87" s="2">
         <v>86</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="3">
         <v>9825095566</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="21">
-      <c r="A88" s="4">
+      <c r="A88" s="2">
         <v>87</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="3">
         <v>7778980004</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="21">
-      <c r="A89" s="4">
+      <c r="A89" s="2">
         <v>88</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="3">
         <v>9924077115</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="21">
-      <c r="A90" s="4">
+      <c r="A90" s="2">
         <v>89</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="3">
         <v>9979892427</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="21">
-      <c r="A91" s="4">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="3">
         <v>9979894053</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="21">
-      <c r="A92" s="4">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="3">
         <v>9979894115</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="18.75">
-      <c r="A93" s="10"/>
-    </row>
-    <row r="94" spans="1:4" ht="18.75">
-      <c r="A94" s="10"/>
+    <row r="93" spans="1:4" ht="21">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="3"/>
+    </row>
+    <row r="94" spans="1:4" ht="21">
+      <c r="A94" s="9">
+        <v>92</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D94" s="11">
+        <v>9924045516</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="21">
+      <c r="A95" s="9">
+        <v>93</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D95" s="11">
+        <v>9724331128</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="21">
+      <c r="A96" s="9">
+        <v>94</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D96" s="11">
+        <v>9586645457</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PHARMA.xlsx
+++ b/PHARMA.xlsx
@@ -1,38 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrutia\Downloads\Validation_GUI\Validation_GUI\Event_Guest_QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2619BA75-5769-4F43-B92A-BD170370FA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="139">
   <si>
     <t>NO</t>
   </si>
@@ -437,12 +425,24 @@
   </si>
   <si>
     <t>DHIRAJKUMAR</t>
+  </si>
+  <si>
+    <t>CHIRAG PATEL</t>
+  </si>
+  <si>
+    <t>ARPIT PATEL</t>
+  </si>
+  <si>
+    <t>JAYMIN JANI</t>
+  </si>
+  <si>
+    <t>XENDER BIOPHARMA &amp; RESEARCH LLP.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -509,7 +509,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -529,13 +529,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -735,7 +728,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -744,7 +737,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1017,17 +1010,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D96"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D99"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.81640625" customWidth="1"/>
+    <col min="2" max="2" width="49.1796875" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" customWidth="1"/>
+    <col min="4" max="4" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75">
+    <row r="1" spans="1:4" ht="18.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1041,7 +1034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75">
+    <row r="2" spans="1:4" ht="18.5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1055,7 +1048,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18.75">
+    <row r="3" spans="1:4" ht="18.5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1069,7 +1062,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18.75">
+    <row r="4" spans="1:4" ht="18.5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1083,7 +1076,7 @@
         <v>8849816883</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18.75">
+    <row r="5" spans="1:4" ht="18.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1097,7 +1090,7 @@
         <v>7359409431</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18.75">
+    <row r="6" spans="1:4" ht="18.5">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1111,7 +1104,7 @@
         <v>7990789429</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18.75">
+    <row r="7" spans="1:4" ht="18.5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1125,7 +1118,7 @@
         <v>9429317767</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18.75">
+    <row r="8" spans="1:4" ht="18.5">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1139,7 +1132,7 @@
         <v>9408233766</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18.75">
+    <row r="9" spans="1:4" ht="18.5">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1153,7 +1146,7 @@
         <v>9601424209</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18.75">
+    <row r="10" spans="1:4" ht="18.5">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1167,7 +1160,7 @@
         <v>8905223389</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18.75">
+    <row r="11" spans="1:4" ht="18.5">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1181,7 +1174,7 @@
         <v>9727783932</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18.75">
+    <row r="12" spans="1:4" ht="18.5">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1195,7 +1188,7 @@
         <v>8200177545</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18.75">
+    <row r="13" spans="1:4" ht="18.5">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1209,7 +1202,7 @@
         <v>9714712264</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18.75">
+    <row r="14" spans="1:4" ht="18.5">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1223,7 +1216,7 @@
         <v>9033399564</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18.75">
+    <row r="15" spans="1:4" ht="18.5">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1237,7 +1230,7 @@
         <v>8140317118</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18.75">
+    <row r="16" spans="1:4" ht="18.5">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1251,7 +1244,7 @@
         <v>9601793913</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18.75">
+    <row r="17" spans="1:4" ht="18.5">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1265,7 +1258,7 @@
         <v>9099661345</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18.75">
+    <row r="18" spans="1:4" ht="18.5">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1279,7 +1272,7 @@
         <v>7600631604</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18.75">
+    <row r="19" spans="1:4" ht="18.5">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1293,7 +1286,7 @@
         <v>8780856496</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75">
+    <row r="20" spans="1:4" ht="18.5">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1307,7 +1300,7 @@
         <v>9377661345</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18.75">
+    <row r="21" spans="1:4" ht="18.5">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1321,7 +1314,7 @@
         <v>9586299911</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18.75">
+    <row r="22" spans="1:4" ht="18.5">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1335,7 +1328,7 @@
         <v>9825748241</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18.75">
+    <row r="23" spans="1:4" ht="18.5">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1349,7 +1342,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18.75">
+    <row r="24" spans="1:4" ht="18.5">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1363,7 +1356,7 @@
         <v>9909006684</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18.75">
+    <row r="25" spans="1:4" ht="18.5">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1377,7 +1370,7 @@
         <v>9909026634</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18.75">
+    <row r="26" spans="1:4" ht="18.5">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1391,7 +1384,7 @@
         <v>8758671797</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18.75">
+    <row r="27" spans="1:4" ht="18.5">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1405,7 +1398,7 @@
         <v>9662779020</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18.75">
+    <row r="28" spans="1:4" ht="18.5">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1419,7 +1412,7 @@
         <v>9558780330</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18.75">
+    <row r="29" spans="1:4" ht="18.5">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1433,7 +1426,7 @@
         <v>9638030812</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18.75">
+    <row r="30" spans="1:4" ht="18.5">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1447,7 +1440,7 @@
         <v>6355485050</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18.75">
+    <row r="31" spans="1:4" ht="18.5">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1461,7 +1454,7 @@
         <v>7600459222</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18.75">
+    <row r="32" spans="1:4" ht="18.5">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1475,7 +1468,7 @@
         <v>9725057586</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18.75">
+    <row r="33" spans="1:4" ht="18.5">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1489,7 +1482,7 @@
         <v>9099928060</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18.75">
+    <row r="34" spans="1:4" ht="18.5">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1503,7 +1496,7 @@
         <v>8140814093</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18.75">
+    <row r="35" spans="1:4" ht="18.5">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1517,7 +1510,7 @@
         <v>9510882026</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18.75">
+    <row r="36" spans="1:4" ht="18.5">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1531,7 +1524,7 @@
         <v>8511746611</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18.75">
+    <row r="37" spans="1:4" ht="18.5">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1545,7 +1538,7 @@
         <v>9099041004</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18.75">
+    <row r="38" spans="1:4" ht="18.5">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1559,7 +1552,7 @@
         <v>9429347065</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18.75">
+    <row r="39" spans="1:4" ht="18.5">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1573,7 +1566,7 @@
         <v>9537515515</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18.75">
+    <row r="40" spans="1:4" ht="18.5">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1587,7 +1580,7 @@
         <v>9998326804</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18.75">
+    <row r="41" spans="1:4" ht="18.5">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1601,7 +1594,7 @@
         <v>9979861157</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18.75">
+    <row r="42" spans="1:4" ht="18.5">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1615,7 +1608,7 @@
         <v>9979953555</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18.75">
+    <row r="43" spans="1:4" ht="18.5">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1629,7 +1622,7 @@
         <v>7096127811</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18.75">
+    <row r="44" spans="1:4" ht="18.5">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1643,7 +1636,7 @@
         <v>9638725303</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18.75">
+    <row r="45" spans="1:4" ht="18.5">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1657,7 +1650,7 @@
         <v>8155005405</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18.75">
+    <row r="46" spans="1:4" ht="18.5">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1671,7 +1664,7 @@
         <v>7665601410</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18.75">
+    <row r="47" spans="1:4" ht="18.5">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -1685,7 +1678,7 @@
         <v>9023868821</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18.75">
+    <row r="48" spans="1:4" ht="18.5">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -1699,7 +1692,7 @@
         <v>9737371486</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18.75">
+    <row r="49" spans="1:4" ht="18.5">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -1713,7 +1706,7 @@
         <v>9428948866</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18.75">
+    <row r="50" spans="1:4" ht="18.5">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -1727,7 +1720,7 @@
         <v>9998800079</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18.75">
+    <row r="51" spans="1:4" ht="18.5">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -1741,7 +1734,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18.75">
+    <row r="52" spans="1:4" ht="18.5">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -1755,7 +1748,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18.75">
+    <row r="53" spans="1:4" ht="18.5">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -1769,7 +1762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18.75">
+    <row r="54" spans="1:4" ht="18.5">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -1783,7 +1776,7 @@
         <v>8238372625</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18.75">
+    <row r="55" spans="1:4" ht="18.5">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -1797,7 +1790,7 @@
         <v>9016625687</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18.75">
+    <row r="56" spans="1:4" ht="18.5">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -1811,7 +1804,7 @@
         <v>7728883118</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18.75">
+    <row r="57" spans="1:4" ht="18.5">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -1825,7 +1818,7 @@
         <v>9998900330</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18.75">
+    <row r="58" spans="1:4" ht="18.5">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -1839,7 +1832,7 @@
         <v>9979887992</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18.75">
+    <row r="59" spans="1:4" ht="18.5">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -1853,7 +1846,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18.75">
+    <row r="60" spans="1:4" ht="18.5">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -1867,7 +1860,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18.75">
+    <row r="61" spans="1:4" ht="18.5">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -1881,7 +1874,7 @@
         <v>9925171610</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18.75">
+    <row r="62" spans="1:4" ht="18.5">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -1895,7 +1888,7 @@
         <v>9879607422</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18.75">
+    <row r="63" spans="1:4" ht="18.5">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -1909,7 +1902,7 @@
         <v>9727768173</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18.75">
+    <row r="64" spans="1:4" ht="18.5">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -1923,7 +1916,7 @@
         <v>9727713871</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="18.75">
+    <row r="65" spans="1:4" ht="18.5">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -1937,7 +1930,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="18.75">
+    <row r="66" spans="1:4" ht="18.5">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -1951,7 +1944,7 @@
         <v>9723553601</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="18.75">
+    <row r="67" spans="1:4" ht="18.5">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -1965,7 +1958,7 @@
         <v>9033301948</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="18.75">
+    <row r="68" spans="1:4" ht="18.5">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -1979,7 +1972,7 @@
         <v>8511154494</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="18.75">
+    <row r="69" spans="1:4" ht="18.5">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -1993,7 +1986,7 @@
         <v>8655924713</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="18.75">
+    <row r="70" spans="1:4" ht="18.5">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2007,7 +2000,7 @@
         <v>9099304021</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="18.75">
+    <row r="71" spans="1:4" ht="18.5">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2021,7 +2014,7 @@
         <v>6351930489</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="18.75">
+    <row r="72" spans="1:4" ht="18.5">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2035,7 +2028,7 @@
         <v>8347912781</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="18.75">
+    <row r="73" spans="1:4" ht="18.5">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2049,7 +2042,7 @@
         <v>7016839757</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="18.75">
+    <row r="74" spans="1:4" ht="18.5">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2063,7 +2056,7 @@
         <v>8866265062</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="18.75">
+    <row r="75" spans="1:4" ht="18.5">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2077,7 +2070,7 @@
         <v>9722435747</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="18.75">
+    <row r="76" spans="1:4" ht="18.5">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2091,7 +2084,7 @@
         <v>7874929252</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="18.75">
+    <row r="77" spans="1:4" ht="18.5">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2105,7 +2098,7 @@
         <v>9537742166</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="18.75">
+    <row r="78" spans="1:4" ht="18.5">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2119,7 +2112,7 @@
         <v>9427607958</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="18.75">
+    <row r="79" spans="1:4" ht="18.5">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2133,7 +2126,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="18.75">
+    <row r="80" spans="1:4" ht="18.5">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2147,7 +2140,7 @@
         <v>9033495028</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="18.75">
+    <row r="81" spans="1:4" ht="18.5">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2322,45 +2315,87 @@
       <c r="D93" s="3"/>
     </row>
     <row r="94" spans="1:4" ht="21">
-      <c r="A94" s="9">
+      <c r="A94" s="2">
         <v>92</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="3">
         <v>9924045516</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="21">
-      <c r="A95" s="9">
+      <c r="A95" s="2">
         <v>93</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C95" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="3">
         <v>9724331128</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="21">
-      <c r="A96" s="9">
+      <c r="A96" s="2">
         <v>94</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="3">
         <v>9586645457</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="21">
+      <c r="A97" s="2">
+        <v>95</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D97" s="3">
+        <v>9099878910</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="21">
+      <c r="A98" s="2">
+        <v>96</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D98" s="3">
+        <v>7874124365</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="21">
+      <c r="A99" s="2">
+        <v>97</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" s="3">
+        <v>7405457218</v>
       </c>
     </row>
   </sheetData>

--- a/PHARMA.xlsx
+++ b/PHARMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrutia\Downloads\Validation_GUI\Validation_GUI\Event_Guest_QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2619BA75-5769-4F43-B92A-BD170370FA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA558C8E-D05E-49DF-97AD-D47ADA03084E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="145">
   <si>
     <t>NO</t>
   </si>
@@ -437,6 +437,24 @@
   </si>
   <si>
     <t>XENDER BIOPHARMA &amp; RESEARCH LLP.</t>
+  </si>
+  <si>
+    <t>KREIOS PHARMA</t>
+  </si>
+  <si>
+    <t>81286 51193</t>
+  </si>
+  <si>
+    <t>95376 36331</t>
+  </si>
+  <si>
+    <t>Mr Manoj Ranade</t>
+  </si>
+  <si>
+    <t>Mr Bipin Patel</t>
+  </si>
+  <si>
+    <t>Mr Hitesh Agarwal</t>
   </si>
 </sst>
 </file>
@@ -480,7 +498,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -503,13 +521,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -530,6 +559,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1011,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6.81640625" customWidth="1"/>
@@ -2398,6 +2430,48 @@
         <v>7405457218</v>
       </c>
     </row>
+    <row r="100" spans="1:4" ht="21">
+      <c r="A100" s="9">
+        <v>98</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D100" s="3">
+        <v>9601276028</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="21">
+      <c r="A101" s="9">
+        <v>99</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="21">
+      <c r="A102" s="9">
+        <v>100</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
